--- a/Seguimiento Validación 2026 (1).xlsx
+++ b/Seguimiento Validación 2026 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ahospinal\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A67635CF-DEE3-4F86-AEFE-E055698FC1D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C0FB66C-DA25-456E-B8E6-20C76D26994B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="1710" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,11 +17,11 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hoja 1'!$A$1:$AI$50</definedName>
-    <definedName name="Z_5B33E207_6C7E_4784_AB5B_324343183027_.wvu.FilterData" localSheetId="0" hidden="1">'Hoja 1'!$A$1:$AI$50</definedName>
+    <definedName name="Z_26D35CE0_3552_4024_AF91_D14582E49002_.wvu.FilterData" localSheetId="0" hidden="1">'Hoja 1'!$A$1:$AI$50</definedName>
   </definedNames>
   <calcPr calcId="0"/>
   <customWorkbookViews>
-    <customWorkbookView name="wrojasa" guid="{5B33E207-6C7E-4784-AB5B-324343183027}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="wrojasa" guid="{26D35CE0-3552-4024-AF91-D14582E49002}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
   </customWorkbookViews>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
@@ -3632,7 +3632,7 @@
         <v>46295</v>
       </c>
       <c r="S11" s="42">
-        <v>46298</v>
+        <v>46301</v>
       </c>
       <c r="T11" s="18"/>
       <c r="U11" s="28" t="s">
@@ -4386,7 +4386,7 @@
         <v>46300</v>
       </c>
       <c r="S19" s="42">
-        <v>46303</v>
+        <v>46300</v>
       </c>
       <c r="T19" s="18"/>
       <c r="U19" s="28" t="s">
@@ -4953,7 +4953,7 @@
         <v>252</v>
       </c>
       <c r="S26" s="69">
-        <v>46307</v>
+        <v>46309</v>
       </c>
       <c r="T26" s="61"/>
       <c r="U26" s="58" t="s">
@@ -5788,7 +5788,7 @@
         <v>46311</v>
       </c>
       <c r="S35" s="139">
-        <v>46314</v>
+        <v>46319</v>
       </c>
       <c r="T35" s="61"/>
       <c r="U35" s="58" t="s">
@@ -42259,9 +42259,9 @@
   </sheetData>
   <autoFilter ref="A1:AI50" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <customSheetViews>
-    <customSheetView guid="{5B33E207-6C7E-4784-AB5B-324343183027}" filter="1" showAutoFilter="1">
+    <customSheetView guid="{26D35CE0-3552-4024-AF91-D14582E49002}" filter="1" showAutoFilter="1">
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="A1:AO50" xr:uid="{BB26F137-27A3-4808-8C6C-46AC543D27CB}"/>
+      <autoFilter ref="A1:AO50" xr:uid="{87C3EFDB-B823-471E-97BE-D4C45C4F0129}"/>
       <extLst>
         <ext uri="GoogleSheetsCustomDataVersion1">
           <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" filterViewId="2096190348"/>

--- a/Seguimiento Validación 2026 (1).xlsx
+++ b/Seguimiento Validación 2026 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ahospinal\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C0FB66C-DA25-456E-B8E6-20C76D26994B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E35DC88-E79C-486A-8D82-2FD0416353BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="1710" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,11 +17,11 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hoja 1'!$A$1:$AI$50</definedName>
-    <definedName name="Z_26D35CE0_3552_4024_AF91_D14582E49002_.wvu.FilterData" localSheetId="0" hidden="1">'Hoja 1'!$A$1:$AI$50</definedName>
+    <definedName name="Z_9E497E7A_F7E9_4680_B50F_6A4CBBC03B62_.wvu.FilterData" localSheetId="0" hidden="1">'Hoja 1'!$A$1:$AI$50</definedName>
   </definedNames>
   <calcPr calcId="0"/>
   <customWorkbookViews>
-    <customWorkbookView name="wrojasa" guid="{26D35CE0-3552-4024-AF91-D14582E49002}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="wrojasa" guid="{9E497E7A-F7E9-4680-B50F-6A4CBBC03B62}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
   </customWorkbookViews>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
@@ -4386,7 +4386,7 @@
         <v>46300</v>
       </c>
       <c r="S19" s="42">
-        <v>46300</v>
+        <v>46305</v>
       </c>
       <c r="T19" s="18"/>
       <c r="U19" s="28" t="s">
@@ -4595,7 +4595,7 @@
       <c r="AH21" s="90"/>
       <c r="AI21" s="90"/>
     </row>
-    <row r="22" spans="1:35" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:35" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="94" t="s">
         <v>34</v>
       </c>
@@ -4676,7 +4676,7 @@
       <c r="AH22" s="112"/>
       <c r="AI22" s="112"/>
     </row>
-    <row r="23" spans="1:35" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:35" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="94"/>
       <c r="B23" s="31"/>
       <c r="C23" s="18"/>
@@ -42259,9 +42259,9 @@
   </sheetData>
   <autoFilter ref="A1:AI50" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <customSheetViews>
-    <customSheetView guid="{26D35CE0-3552-4024-AF91-D14582E49002}" filter="1" showAutoFilter="1">
+    <customSheetView guid="{9E497E7A-F7E9-4680-B50F-6A4CBBC03B62}" filter="1" showAutoFilter="1">
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="A1:AO50" xr:uid="{87C3EFDB-B823-471E-97BE-D4C45C4F0129}"/>
+      <autoFilter ref="A1:AO50" xr:uid="{F3F74825-3EA0-4B8B-A74F-88597FA80918}"/>
       <extLst>
         <ext uri="GoogleSheetsCustomDataVersion1">
           <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" filterViewId="2096190348"/>
